--- a/ETF Summary Report.xlsx
+++ b/ETF Summary Report.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manthan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF3485B9-A503-5545-A829-FAAECF4627F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B8AC532-EAD6-CD40-A132-40A06B8F8140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Manthan" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -24,6 +24,7 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>SR. NO.</t>
   </si>
@@ -55,12 +56,6 @@
     <t>AUTOIETF</t>
   </si>
   <si>
-    <t>ICICI Prudential Nifty Bank ETF</t>
-  </si>
-  <si>
-    <t>BANKIETF</t>
-  </si>
-  <si>
     <t>ICICI Prudential Nifty Commodities ETF</t>
   </si>
   <si>
@@ -205,12 +200,6 @@
     <t>PVTBANIETF</t>
   </si>
   <si>
-    <t>ICICI Prudential BSE Sensex ETF</t>
-  </si>
-  <si>
-    <t>SENSEXIETF</t>
-  </si>
-  <si>
     <t>Tata Nifty India Digital ETF</t>
   </si>
   <si>
@@ -227,18 +216,6 @@
   </si>
   <si>
     <t>Kotak Nifty Chemicals ETF</t>
-  </si>
-  <si>
-    <t>GOLDIETF</t>
-  </si>
-  <si>
-    <t>SILVERIETF</t>
-  </si>
-  <si>
-    <t>ICICI Prudential Gold ETF</t>
-  </si>
-  <si>
-    <t>ICICI Prudential Silver ETF</t>
   </si>
 </sst>
 </file>
@@ -299,7 +276,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -307,8 +284,6 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1439,7 +1414,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="1" customWidth="1"/>
@@ -1477,10 +1452,10 @@
         <v>6</v>
       </c>
       <c r="D2" s="5">
-        <v>6754</v>
+        <v>143</v>
       </c>
       <c r="E2" s="6">
-        <v>28.69</v>
+        <v>29.05</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1494,10 +1469,10 @@
         <v>8</v>
       </c>
       <c r="D3" s="5">
-        <v>2987</v>
+        <v>123</v>
       </c>
       <c r="E3" s="6">
-        <v>61.2</v>
+        <v>101.24</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1511,10 +1486,10 @@
         <v>10</v>
       </c>
       <c r="D4" s="5">
-        <v>5405</v>
+        <v>17</v>
       </c>
       <c r="E4" s="6">
-        <v>93.85</v>
+        <v>119.9</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1528,10 +1503,10 @@
         <v>12</v>
       </c>
       <c r="D5" s="5">
-        <v>694</v>
+        <v>205</v>
       </c>
       <c r="E5" s="6">
-        <v>128.12</v>
+        <v>102.99</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1545,10 +1520,10 @@
         <v>14</v>
       </c>
       <c r="D6" s="5">
-        <v>1415</v>
+        <v>85</v>
       </c>
       <c r="E6" s="6">
-        <v>93.44</v>
+        <v>24.75</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1562,10 +1537,10 @@
         <v>16</v>
       </c>
       <c r="D7" s="5">
-        <v>18371</v>
+        <v>112</v>
       </c>
       <c r="E7" s="6">
-        <v>24.29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1579,10 +1554,10 @@
         <v>18</v>
       </c>
       <c r="D8" s="5">
-        <v>17050</v>
+        <v>140</v>
       </c>
       <c r="E8" s="6">
-        <v>31.46</v>
+        <v>32.32</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1596,10 +1571,10 @@
         <v>20</v>
       </c>
       <c r="D9" s="5">
-        <v>11508</v>
+        <v>36</v>
       </c>
       <c r="E9" s="6">
-        <v>32.76</v>
+        <v>54.97</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1613,15 +1588,15 @@
         <v>22</v>
       </c>
       <c r="D10" s="5">
-        <v>3547</v>
+        <v>16</v>
       </c>
       <c r="E10" s="6">
-        <v>59.22</v>
+        <v>154.41</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>23</v>
@@ -1630,15 +1605,15 @@
         <v>24</v>
       </c>
       <c r="D11" s="5">
-        <v>486</v>
+        <v>21</v>
       </c>
       <c r="E11" s="6">
-        <v>152.38999999999999</v>
+        <v>98.05</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>25</v>
@@ -1647,15 +1622,15 @@
         <v>26</v>
       </c>
       <c r="D12" s="5">
-        <v>3491</v>
+        <v>118</v>
       </c>
       <c r="E12" s="6">
-        <v>98.96</v>
+        <v>33.79</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>27</v>
@@ -1664,15 +1639,15 @@
         <v>28</v>
       </c>
       <c r="D13" s="5">
-        <v>5090</v>
+        <v>130</v>
       </c>
       <c r="E13" s="6">
-        <v>41.23</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>29</v>
@@ -1681,15 +1656,15 @@
         <v>30</v>
       </c>
       <c r="D14" s="5">
-        <v>1884</v>
+        <v>21</v>
       </c>
       <c r="E14" s="6">
-        <v>155.01</v>
+        <v>70.44</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>31</v>
@@ -1698,15 +1673,15 @@
         <v>32</v>
       </c>
       <c r="D15" s="5">
-        <v>470</v>
+        <v>848</v>
       </c>
       <c r="E15" s="6">
-        <v>71.17</v>
+        <v>12.31</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>33</v>
@@ -1715,15 +1690,15 @@
         <v>34</v>
       </c>
       <c r="D16" s="5">
-        <v>15372</v>
+        <v>90</v>
       </c>
       <c r="E16" s="6">
-        <v>10.53</v>
+        <v>22.59</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>35</v>
@@ -1732,15 +1707,15 @@
         <v>36</v>
       </c>
       <c r="D17" s="5">
-        <v>20131</v>
+        <v>135</v>
       </c>
       <c r="E17" s="6">
-        <v>23.09</v>
+        <v>32.71</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>37</v>
@@ -1749,15 +1724,15 @@
         <v>38</v>
       </c>
       <c r="D18" s="5">
-        <v>2715</v>
+        <v>224</v>
       </c>
       <c r="E18" s="6">
-        <v>31.17</v>
+        <v>89.31</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>39</v>
@@ -1766,15 +1741,15 @@
         <v>40</v>
       </c>
       <c r="D19" s="5">
-        <v>1505</v>
+        <v>34</v>
       </c>
       <c r="E19" s="6">
-        <v>88.23</v>
+        <v>224.5</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>41</v>
@@ -1783,15 +1758,15 @@
         <v>42</v>
       </c>
       <c r="D20" s="5">
-        <v>572</v>
+        <v>85</v>
       </c>
       <c r="E20" s="6">
-        <v>233.06</v>
+        <v>23.69</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>43</v>
@@ -1800,15 +1775,15 @@
         <v>44</v>
       </c>
       <c r="D21" s="5">
-        <v>16598</v>
+        <v>25</v>
       </c>
       <c r="E21" s="6">
-        <v>24.39</v>
+        <v>78.22</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>45</v>
@@ -1817,15 +1792,15 @@
         <v>46</v>
       </c>
       <c r="D22" s="5">
-        <v>1158</v>
+        <v>127</v>
       </c>
       <c r="E22" s="6">
-        <v>89</v>
+        <v>16.02</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>47</v>
@@ -1834,15 +1809,15 @@
         <v>48</v>
       </c>
       <c r="D23" s="5">
-        <v>6186</v>
+        <v>7</v>
       </c>
       <c r="E23" s="6">
-        <v>16.82</v>
+        <v>284</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>49</v>
@@ -1851,15 +1826,15 @@
         <v>50</v>
       </c>
       <c r="D24" s="5">
-        <v>1376</v>
+        <v>169</v>
       </c>
       <c r="E24" s="6">
-        <v>294.5</v>
+        <v>12.39</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>51</v>
@@ -1868,15 +1843,15 @@
         <v>52</v>
       </c>
       <c r="D25" s="5">
-        <v>13307</v>
+        <v>220</v>
       </c>
       <c r="E25" s="6">
-        <v>12.2</v>
+        <v>99.46</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>53</v>
@@ -1885,15 +1860,15 @@
         <v>54</v>
       </c>
       <c r="D26" s="5">
-        <v>5250</v>
+        <v>403</v>
       </c>
       <c r="E26" s="6">
-        <v>86.71</v>
+        <v>28.86</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>55</v>
@@ -1902,112 +1877,44 @@
         <v>56</v>
       </c>
       <c r="D27" s="5">
-        <v>7558</v>
+        <v>21</v>
       </c>
       <c r="E27" s="6">
-        <v>28.97</v>
+        <v>83.88</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C28" s="4" t="s">
-        <v>58</v>
-      </c>
       <c r="D28" s="5">
-        <v>482</v>
+        <v>209</v>
       </c>
       <c r="E28" s="6">
-        <v>978.51</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D29" s="5">
-        <v>847</v>
+        <v>72</v>
       </c>
       <c r="E29" s="6">
-        <v>98.22</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="3">
-        <v>31</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D30" s="5">
-        <v>418</v>
-      </c>
-      <c r="E30" s="6">
-        <v>9.68</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="3">
-        <v>32</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D31" s="5">
-        <v>144</v>
-      </c>
-      <c r="E31" s="6">
-        <v>27.81</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="3">
-        <v>33</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D32" s="7">
-        <v>201</v>
-      </c>
-      <c r="E32" s="7">
-        <v>123.86</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="3">
-        <v>34</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D33" s="7">
-        <v>108</v>
-      </c>
-      <c r="E33" s="7">
-        <v>229.98</v>
+        <v>28.4</v>
       </c>
     </row>
   </sheetData>

--- a/ETF Summary Report.xlsx
+++ b/ETF Summary Report.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manthan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B8AC532-EAD6-CD40-A132-40A06B8F8140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{130D038A-AE81-584A-AEFB-A9A676BB2F92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Manthan" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -276,14 +279,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -367,6 +369,353 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="positions"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="B2" t="str">
+            <v>AUTOIETF</v>
+          </cell>
+          <cell r="C2">
+            <v>4290</v>
+          </cell>
+          <cell r="D2">
+            <v>28.26</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>BANKIETF</v>
+          </cell>
+          <cell r="C3">
+            <v>2404</v>
+          </cell>
+          <cell r="D3">
+            <v>61.29</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="B4" t="str">
+            <v>CHEMICAL</v>
+          </cell>
+          <cell r="C4">
+            <v>1552</v>
+          </cell>
+          <cell r="D4">
+            <v>27.6</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="B5" t="str">
+            <v>COMMOIETF</v>
+          </cell>
+          <cell r="C5">
+            <v>1622</v>
+          </cell>
+          <cell r="D5">
+            <v>99.99</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="B6" t="str">
+            <v>CONSUMIETF</v>
+          </cell>
+          <cell r="C6">
+            <v>200</v>
+          </cell>
+          <cell r="D6">
+            <v>117.18</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="B7" t="str">
+            <v>CPSEETF</v>
+          </cell>
+          <cell r="C7">
+            <v>2006</v>
+          </cell>
+          <cell r="D7">
+            <v>102.29</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="B8" t="str">
+            <v>ECAPINSURE</v>
+          </cell>
+          <cell r="C8">
+            <v>3620</v>
+          </cell>
+          <cell r="D8">
+            <v>23.87</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="B9" t="str">
+            <v>EVINDIA</v>
+          </cell>
+          <cell r="C9">
+            <v>2160</v>
+          </cell>
+          <cell r="D9">
+            <v>30.23</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="B10" t="str">
+            <v>FINIETF</v>
+          </cell>
+          <cell r="C10">
+            <v>2695</v>
+          </cell>
+          <cell r="D10">
+            <v>31.6</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="B11" t="str">
+            <v>FMCGIETF</v>
+          </cell>
+          <cell r="C11">
+            <v>435</v>
+          </cell>
+          <cell r="D11">
+            <v>54.2</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="B12" t="str">
+            <v>GROWWPOWER</v>
+          </cell>
+          <cell r="C12">
+            <v>10530</v>
+          </cell>
+          <cell r="D12">
+            <v>10.38</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="B13" t="str">
+            <v>HEALTHIETF</v>
+          </cell>
+          <cell r="C13">
+            <v>1392</v>
+          </cell>
+          <cell r="D13">
+            <v>151.41</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="B14" t="str">
+            <v>INFRAIETF</v>
+          </cell>
+          <cell r="C14">
+            <v>690</v>
+          </cell>
+          <cell r="D14">
+            <v>95.75</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="B15" t="str">
+            <v>ITIETF</v>
+          </cell>
+          <cell r="C15">
+            <v>705</v>
+          </cell>
+          <cell r="D15">
+            <v>33.369999999999997</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="B16" t="str">
+            <v>MAKEINDIA</v>
+          </cell>
+          <cell r="C16">
+            <v>1135</v>
+          </cell>
+          <cell r="D16">
+            <v>157.82</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="B17" t="str">
+            <v>MASPTOP50</v>
+          </cell>
+          <cell r="C17">
+            <v>700</v>
+          </cell>
+          <cell r="D17">
+            <v>70.16</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="B18" t="str">
+            <v>METALIETF</v>
+          </cell>
+          <cell r="C18">
+            <v>9635</v>
+          </cell>
+          <cell r="D18">
+            <v>12.24</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="B19" t="str">
+            <v>MIDCAPIETF</v>
+          </cell>
+          <cell r="C19">
+            <v>2605</v>
+          </cell>
+          <cell r="D19">
+            <v>22.23</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="B20" t="str">
+            <v>MNC</v>
+          </cell>
+          <cell r="C20">
+            <v>7075</v>
+          </cell>
+          <cell r="D20">
+            <v>32.11</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="B21" t="str">
+            <v>MODEFENCE</v>
+          </cell>
+          <cell r="C21">
+            <v>2406</v>
+          </cell>
+          <cell r="D21">
+            <v>90.08</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="B22" t="str">
+            <v>MON100</v>
+          </cell>
+          <cell r="C22">
+            <v>105</v>
+          </cell>
+          <cell r="D22">
+            <v>222.69</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="B23" t="str">
+            <v>MONIFTY500</v>
+          </cell>
+          <cell r="C23">
+            <v>1221</v>
+          </cell>
+          <cell r="D23">
+            <v>23.35</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="B24" t="str">
+            <v>MOREALTY</v>
+          </cell>
+          <cell r="C24">
+            <v>310</v>
+          </cell>
+          <cell r="D24">
+            <v>76.59</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="B25" t="str">
+            <v>MOSMALL250</v>
+          </cell>
+          <cell r="C25">
+            <v>1505</v>
+          </cell>
+          <cell r="D25">
+            <v>15.66</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="B26" t="str">
+            <v>NIFTYIETF</v>
+          </cell>
+          <cell r="C26">
+            <v>80</v>
+          </cell>
+          <cell r="D26">
+            <v>279.52999999999997</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="B27" t="str">
+            <v>OILIETF</v>
+          </cell>
+          <cell r="C27">
+            <v>4185</v>
+          </cell>
+          <cell r="D27">
+            <v>12.21</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="B28" t="str">
+            <v>PSUBNKIETF</v>
+          </cell>
+          <cell r="C28">
+            <v>1070</v>
+          </cell>
+          <cell r="D28">
+            <v>97.4</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="B29" t="str">
+            <v>PVTBANIETF</v>
+          </cell>
+          <cell r="C29">
+            <v>3735</v>
+          </cell>
+          <cell r="D29">
+            <v>28.51</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="B30" t="str">
+            <v>SENSEXIETF</v>
+          </cell>
+          <cell r="C30">
+            <v>25</v>
+          </cell>
+          <cell r="D30">
+            <v>915.24</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="B31" t="str">
+            <v>TNIDETF</v>
+          </cell>
+          <cell r="C31">
+            <v>290</v>
+          </cell>
+          <cell r="D31">
+            <v>80.83</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1452,10 +1801,12 @@
         <v>6</v>
       </c>
       <c r="D2" s="5">
-        <v>143</v>
-      </c>
-      <c r="E2" s="6">
-        <v>29.05</v>
+        <f>LOOKUP(C2,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
+        <v>4290</v>
+      </c>
+      <c r="E2" s="5">
+        <f>LOOKUP(C2,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
+        <v>28.26</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1469,10 +1820,12 @@
         <v>8</v>
       </c>
       <c r="D3" s="5">
-        <v>123</v>
-      </c>
-      <c r="E3" s="6">
-        <v>101.24</v>
+        <f>LOOKUP(C3,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
+        <v>1622</v>
+      </c>
+      <c r="E3" s="5">
+        <f>LOOKUP(C3,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
+        <v>99.99</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1486,10 +1839,12 @@
         <v>10</v>
       </c>
       <c r="D4" s="5">
-        <v>17</v>
-      </c>
-      <c r="E4" s="6">
-        <v>119.9</v>
+        <f>LOOKUP(C4,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
+        <v>200</v>
+      </c>
+      <c r="E4" s="5">
+        <f>LOOKUP(C4,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
+        <v>117.18</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1503,10 +1858,12 @@
         <v>12</v>
       </c>
       <c r="D5" s="5">
-        <v>205</v>
-      </c>
-      <c r="E5" s="6">
-        <v>102.99</v>
+        <f>LOOKUP(C5,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
+        <v>2006</v>
+      </c>
+      <c r="E5" s="5">
+        <f>LOOKUP(C5,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
+        <v>102.29</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1520,10 +1877,12 @@
         <v>14</v>
       </c>
       <c r="D6" s="5">
-        <v>85</v>
-      </c>
-      <c r="E6" s="6">
-        <v>24.75</v>
+        <f>LOOKUP(C6,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
+        <v>3620</v>
+      </c>
+      <c r="E6" s="5">
+        <f>LOOKUP(C6,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
+        <v>23.87</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1537,10 +1896,12 @@
         <v>16</v>
       </c>
       <c r="D7" s="5">
-        <v>112</v>
-      </c>
-      <c r="E7" s="6">
-        <v>31</v>
+        <f>LOOKUP(C7,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
+        <v>2160</v>
+      </c>
+      <c r="E7" s="5">
+        <f>LOOKUP(C7,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
+        <v>30.23</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1554,10 +1915,12 @@
         <v>18</v>
       </c>
       <c r="D8" s="5">
-        <v>140</v>
-      </c>
-      <c r="E8" s="6">
-        <v>32.32</v>
+        <f>LOOKUP(C8,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
+        <v>2695</v>
+      </c>
+      <c r="E8" s="5">
+        <f>LOOKUP(C8,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
+        <v>31.6</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1571,10 +1934,12 @@
         <v>20</v>
       </c>
       <c r="D9" s="5">
-        <v>36</v>
-      </c>
-      <c r="E9" s="6">
-        <v>54.97</v>
+        <f>LOOKUP(C9,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
+        <v>435</v>
+      </c>
+      <c r="E9" s="5">
+        <f>LOOKUP(C9,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
+        <v>54.2</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1588,10 +1953,12 @@
         <v>22</v>
       </c>
       <c r="D10" s="5">
-        <v>16</v>
-      </c>
-      <c r="E10" s="6">
-        <v>154.41</v>
+        <f>LOOKUP(C10,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
+        <v>1392</v>
+      </c>
+      <c r="E10" s="5">
+        <f>LOOKUP(C10,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
+        <v>151.41</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1605,10 +1972,12 @@
         <v>24</v>
       </c>
       <c r="D11" s="5">
-        <v>21</v>
-      </c>
-      <c r="E11" s="6">
-        <v>98.05</v>
+        <f>LOOKUP(C11,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
+        <v>690</v>
+      </c>
+      <c r="E11" s="5">
+        <f>LOOKUP(C11,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
+        <v>95.75</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1622,10 +1991,12 @@
         <v>26</v>
       </c>
       <c r="D12" s="5">
-        <v>118</v>
-      </c>
-      <c r="E12" s="6">
-        <v>33.79</v>
+        <f>LOOKUP(C12,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
+        <v>705</v>
+      </c>
+      <c r="E12" s="5">
+        <f>LOOKUP(C12,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
+        <v>33.369999999999997</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1639,10 +2010,12 @@
         <v>28</v>
       </c>
       <c r="D13" s="5">
-        <v>130</v>
-      </c>
-      <c r="E13" s="6">
-        <v>160</v>
+        <f>LOOKUP(C13,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
+        <v>1135</v>
+      </c>
+      <c r="E13" s="5">
+        <f>LOOKUP(C13,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
+        <v>157.82</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1656,10 +2029,12 @@
         <v>30</v>
       </c>
       <c r="D14" s="5">
-        <v>21</v>
-      </c>
-      <c r="E14" s="6">
-        <v>70.44</v>
+        <f>LOOKUP(C14,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
+        <v>700</v>
+      </c>
+      <c r="E14" s="5">
+        <f>LOOKUP(C14,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
+        <v>70.16</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1673,10 +2048,12 @@
         <v>32</v>
       </c>
       <c r="D15" s="5">
-        <v>848</v>
-      </c>
-      <c r="E15" s="6">
-        <v>12.31</v>
+        <f>LOOKUP(C15,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
+        <v>9635</v>
+      </c>
+      <c r="E15" s="5">
+        <f>LOOKUP(C15,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
+        <v>12.24</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1690,10 +2067,12 @@
         <v>34</v>
       </c>
       <c r="D16" s="5">
-        <v>90</v>
-      </c>
-      <c r="E16" s="6">
-        <v>22.59</v>
+        <f>LOOKUP(C16,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
+        <v>2605</v>
+      </c>
+      <c r="E16" s="5">
+        <f>LOOKUP(C16,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
+        <v>22.23</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1707,10 +2086,12 @@
         <v>36</v>
       </c>
       <c r="D17" s="5">
-        <v>135</v>
-      </c>
-      <c r="E17" s="6">
-        <v>32.71</v>
+        <f>LOOKUP(C17,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
+        <v>7075</v>
+      </c>
+      <c r="E17" s="5">
+        <f>LOOKUP(C17,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
+        <v>32.11</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1724,10 +2105,12 @@
         <v>38</v>
       </c>
       <c r="D18" s="5">
-        <v>224</v>
-      </c>
-      <c r="E18" s="6">
-        <v>89.31</v>
+        <f>LOOKUP(C18,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
+        <v>2406</v>
+      </c>
+      <c r="E18" s="5">
+        <f>LOOKUP(C18,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
+        <v>90.08</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1741,10 +2124,12 @@
         <v>40</v>
       </c>
       <c r="D19" s="5">
-        <v>34</v>
-      </c>
-      <c r="E19" s="6">
-        <v>224.5</v>
+        <f>LOOKUP(C19,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
+        <v>105</v>
+      </c>
+      <c r="E19" s="5">
+        <f>LOOKUP(C19,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
+        <v>222.69</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1758,10 +2143,12 @@
         <v>42</v>
       </c>
       <c r="D20" s="5">
-        <v>85</v>
-      </c>
-      <c r="E20" s="6">
-        <v>23.69</v>
+        <f>LOOKUP(C20,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
+        <v>1221</v>
+      </c>
+      <c r="E20" s="5">
+        <f>LOOKUP(C20,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
+        <v>23.35</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1775,10 +2162,12 @@
         <v>44</v>
       </c>
       <c r="D21" s="5">
-        <v>25</v>
-      </c>
-      <c r="E21" s="6">
-        <v>78.22</v>
+        <f>LOOKUP(C21,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
+        <v>310</v>
+      </c>
+      <c r="E21" s="5">
+        <f>LOOKUP(C21,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
+        <v>76.59</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1792,10 +2181,12 @@
         <v>46</v>
       </c>
       <c r="D22" s="5">
-        <v>127</v>
-      </c>
-      <c r="E22" s="6">
-        <v>16.02</v>
+        <f>LOOKUP(C22,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
+        <v>1505</v>
+      </c>
+      <c r="E22" s="5">
+        <f>LOOKUP(C22,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
+        <v>15.66</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1809,10 +2200,12 @@
         <v>48</v>
       </c>
       <c r="D23" s="5">
-        <v>7</v>
-      </c>
-      <c r="E23" s="6">
-        <v>284</v>
+        <f>LOOKUP(C23,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
+        <v>80</v>
+      </c>
+      <c r="E23" s="5">
+        <f>LOOKUP(C23,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
+        <v>279.52999999999997</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1826,10 +2219,12 @@
         <v>50</v>
       </c>
       <c r="D24" s="5">
-        <v>169</v>
-      </c>
-      <c r="E24" s="6">
-        <v>12.39</v>
+        <f>LOOKUP(C24,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
+        <v>4185</v>
+      </c>
+      <c r="E24" s="5">
+        <f>LOOKUP(C24,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
+        <v>12.21</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1843,10 +2238,12 @@
         <v>52</v>
       </c>
       <c r="D25" s="5">
-        <v>220</v>
-      </c>
-      <c r="E25" s="6">
-        <v>99.46</v>
+        <f>LOOKUP(C25,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
+        <v>1070</v>
+      </c>
+      <c r="E25" s="5">
+        <f>LOOKUP(C25,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
+        <v>97.4</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1860,10 +2257,12 @@
         <v>54</v>
       </c>
       <c r="D26" s="5">
-        <v>403</v>
-      </c>
-      <c r="E26" s="6">
-        <v>28.86</v>
+        <f>LOOKUP(C26,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
+        <v>3735</v>
+      </c>
+      <c r="E26" s="5">
+        <f>LOOKUP(C26,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
+        <v>28.51</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1877,10 +2276,12 @@
         <v>56</v>
       </c>
       <c r="D27" s="5">
-        <v>21</v>
-      </c>
-      <c r="E27" s="6">
-        <v>83.88</v>
+        <f>LOOKUP(C27,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
+        <v>290</v>
+      </c>
+      <c r="E27" s="5">
+        <f>LOOKUP(C27,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
+        <v>80.83</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1894,10 +2295,12 @@
         <v>57</v>
       </c>
       <c r="D28" s="5">
-        <v>209</v>
-      </c>
-      <c r="E28" s="6">
-        <v>10.6</v>
+        <f>LOOKUP(C28,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
+        <v>10530</v>
+      </c>
+      <c r="E28" s="5">
+        <f>LOOKUP(C28,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
+        <v>10.38</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1911,10 +2314,12 @@
         <v>58</v>
       </c>
       <c r="D29" s="5">
-        <v>72</v>
-      </c>
-      <c r="E29" s="6">
-        <v>28.4</v>
+        <f>LOOKUP(C29,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
+        <v>1552</v>
+      </c>
+      <c r="E29" s="5">
+        <f>LOOKUP(C29,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
+        <v>27.6</v>
       </c>
     </row>
   </sheetData>

--- a/ETF Summary Report.xlsx
+++ b/ETF Summary Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manthan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{130D038A-AE81-584A-AEFB-A9A676BB2F92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EAC9361-2EAE-914A-B801-D6B2D436BC55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="63">
   <si>
     <t>SR. NO.</t>
   </si>
@@ -219,6 +219,12 @@
   </si>
   <si>
     <t>Kotak Nifty Chemicals ETF</t>
+  </si>
+  <si>
+    <t>BANKIETF</t>
+  </si>
+  <si>
+    <t>SENSEXIETF</t>
   </si>
 </sst>
 </file>
@@ -1763,7 +1769,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="1" customWidth="1"/>
@@ -2322,6 +2328,44 @@
         <v>27.6</v>
       </c>
     </row>
+    <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="3">
+        <v>28</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D30" s="5">
+        <f>LOOKUP(C30,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
+        <v>25</v>
+      </c>
+      <c r="E30" s="5">
+        <f>LOOKUP(C30,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
+        <v>915.24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="3">
+        <v>28</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D31" s="5">
+        <f>LOOKUP(C31,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
+        <v>2404</v>
+      </c>
+      <c r="E31" s="5">
+        <f>LOOKUP(C31,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
+        <v>61.29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>

--- a/ETF Summary Report.xlsx
+++ b/ETF Summary Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manthan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EAC9361-2EAE-914A-B801-D6B2D436BC55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0C49126-971E-B74D-B57C-533E6988AF41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -285,13 +285,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -389,333 +390,333 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
-          <cell r="B2" t="str">
+          <cell r="O2" t="str">
             <v>AUTOIETF</v>
           </cell>
-          <cell r="C2">
-            <v>4290</v>
-          </cell>
-          <cell r="D2">
-            <v>28.26</v>
+          <cell r="P2">
+            <v>7871</v>
+          </cell>
+          <cell r="Q2">
+            <v>28.303807648329308</v>
           </cell>
         </row>
         <row r="3">
-          <cell r="B3" t="str">
+          <cell r="O3" t="str">
             <v>BANKIETF</v>
           </cell>
-          <cell r="C3">
-            <v>2404</v>
-          </cell>
-          <cell r="D3">
-            <v>61.29</v>
+          <cell r="P3">
+            <v>4804</v>
+          </cell>
+          <cell r="Q3">
+            <v>61.289999999999992</v>
           </cell>
         </row>
         <row r="4">
-          <cell r="B4" t="str">
+          <cell r="O4" t="str">
             <v>CHEMICAL</v>
           </cell>
-          <cell r="C4">
-            <v>1552</v>
-          </cell>
-          <cell r="D4">
-            <v>27.6</v>
+          <cell r="P4">
+            <v>3172</v>
+          </cell>
+          <cell r="Q4">
+            <v>27.530201765447668</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="B5" t="str">
+          <cell r="O5" t="str">
             <v>COMMOIETF</v>
           </cell>
-          <cell r="C5">
-            <v>1622</v>
-          </cell>
-          <cell r="D5">
-            <v>99.99</v>
+          <cell r="P5">
+            <v>3365</v>
+          </cell>
+          <cell r="Q5">
+            <v>100.12240118870729</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="B6" t="str">
+          <cell r="O6" t="str">
             <v>CONSUMIETF</v>
           </cell>
-          <cell r="C6">
-            <v>200</v>
-          </cell>
-          <cell r="D6">
-            <v>117.18</v>
+          <cell r="P6">
+            <v>493</v>
+          </cell>
+          <cell r="Q6">
+            <v>117.38000000000001</v>
           </cell>
         </row>
         <row r="7">
-          <cell r="B7" t="str">
+          <cell r="O7" t="str">
             <v>CPSEETF</v>
           </cell>
-          <cell r="C7">
-            <v>2006</v>
-          </cell>
-          <cell r="D7">
-            <v>102.29</v>
+          <cell r="P7">
+            <v>4215</v>
+          </cell>
+          <cell r="Q7">
+            <v>102.29550415183868</v>
           </cell>
         </row>
         <row r="8">
-          <cell r="B8" t="str">
+          <cell r="O8" t="str">
             <v>ECAPINSURE</v>
           </cell>
-          <cell r="C8">
-            <v>3620</v>
-          </cell>
-          <cell r="D8">
-            <v>23.87</v>
+          <cell r="P8">
+            <v>8163</v>
+          </cell>
+          <cell r="Q8">
+            <v>23.879163297807182</v>
           </cell>
         </row>
         <row r="9">
-          <cell r="B9" t="str">
+          <cell r="O9" t="str">
             <v>EVINDIA</v>
           </cell>
-          <cell r="C9">
-            <v>2160</v>
-          </cell>
-          <cell r="D9">
-            <v>30.23</v>
+          <cell r="P9">
+            <v>4522</v>
+          </cell>
+          <cell r="Q9">
+            <v>30.268575851393187</v>
           </cell>
         </row>
         <row r="10">
-          <cell r="B10" t="str">
+          <cell r="O10" t="str">
             <v>FINIETF</v>
           </cell>
-          <cell r="C10">
-            <v>2695</v>
-          </cell>
-          <cell r="D10">
-            <v>31.6</v>
+          <cell r="P10">
+            <v>5529</v>
+          </cell>
+          <cell r="Q10">
+            <v>31.559750406945195</v>
           </cell>
         </row>
         <row r="11">
-          <cell r="B11" t="str">
+          <cell r="O11" t="str">
             <v>FMCGIETF</v>
           </cell>
-          <cell r="C11">
-            <v>435</v>
-          </cell>
-          <cell r="D11">
-            <v>54.2</v>
+          <cell r="P11">
+            <v>1245</v>
+          </cell>
+          <cell r="Q11">
+            <v>54.28053012048192</v>
           </cell>
         </row>
         <row r="12">
-          <cell r="B12" t="str">
+          <cell r="O12" t="str">
             <v>GROWWPOWER</v>
           </cell>
-          <cell r="C12">
-            <v>10530</v>
-          </cell>
-          <cell r="D12">
-            <v>10.38</v>
+          <cell r="P12">
+            <v>21269</v>
+          </cell>
+          <cell r="Q12">
+            <v>10.362358361935209</v>
           </cell>
         </row>
         <row r="13">
-          <cell r="B13" t="str">
+          <cell r="O13" t="str">
             <v>HEALTHIETF</v>
           </cell>
-          <cell r="C13">
-            <v>1392</v>
-          </cell>
-          <cell r="D13">
-            <v>151.41</v>
+          <cell r="P13">
+            <v>3196</v>
+          </cell>
+          <cell r="Q13">
+            <v>151.8827158948686</v>
           </cell>
         </row>
         <row r="14">
-          <cell r="B14" t="str">
+          <cell r="O14" t="str">
             <v>INFRAIETF</v>
           </cell>
-          <cell r="C14">
-            <v>690</v>
-          </cell>
-          <cell r="D14">
-            <v>95.75</v>
+          <cell r="P14">
+            <v>2625</v>
+          </cell>
+          <cell r="Q14">
+            <v>95.847759999999994</v>
           </cell>
         </row>
         <row r="15">
-          <cell r="B15" t="str">
+          <cell r="O15" t="str">
             <v>ITIETF</v>
           </cell>
-          <cell r="C15">
-            <v>705</v>
-          </cell>
-          <cell r="D15">
-            <v>33.369999999999997</v>
+          <cell r="P15">
+            <v>1687</v>
+          </cell>
+          <cell r="Q15">
+            <v>33.43657972732661</v>
           </cell>
         </row>
         <row r="16">
-          <cell r="B16" t="str">
+          <cell r="O16" t="str">
             <v>MAKEINDIA</v>
           </cell>
-          <cell r="C16">
-            <v>1135</v>
-          </cell>
-          <cell r="D16">
-            <v>157.82</v>
+          <cell r="P16">
+            <v>2111</v>
+          </cell>
+          <cell r="Q16">
+            <v>158.05747513027003</v>
           </cell>
         </row>
         <row r="17">
-          <cell r="B17" t="str">
+          <cell r="O17" t="str">
             <v>MASPTOP50</v>
           </cell>
-          <cell r="C17">
-            <v>700</v>
-          </cell>
-          <cell r="D17">
-            <v>70.16</v>
+          <cell r="P17">
+            <v>3733</v>
+          </cell>
+          <cell r="Q17">
+            <v>69.903037771229577</v>
           </cell>
         </row>
         <row r="18">
-          <cell r="B18" t="str">
+          <cell r="O18" t="str">
             <v>METALIETF</v>
           </cell>
-          <cell r="C18">
-            <v>9635</v>
-          </cell>
-          <cell r="D18">
-            <v>12.24</v>
+          <cell r="P18">
+            <v>22981</v>
+          </cell>
+          <cell r="Q18">
+            <v>12.271476001914625</v>
           </cell>
         </row>
         <row r="19">
-          <cell r="B19" t="str">
+          <cell r="O19" t="str">
             <v>MIDCAPIETF</v>
           </cell>
-          <cell r="C19">
-            <v>2605</v>
-          </cell>
-          <cell r="D19">
-            <v>22.23</v>
+          <cell r="P19">
+            <v>5155</v>
+          </cell>
+          <cell r="Q19">
+            <v>22.226459747817653</v>
           </cell>
         </row>
         <row r="20">
-          <cell r="B20" t="str">
+          <cell r="O20" t="str">
             <v>MNC</v>
           </cell>
-          <cell r="C20">
-            <v>7075</v>
-          </cell>
-          <cell r="D20">
-            <v>32.11</v>
+          <cell r="P20">
+            <v>11452</v>
+          </cell>
+          <cell r="Q20">
+            <v>32.156601466992662</v>
           </cell>
         </row>
         <row r="21">
-          <cell r="B21" t="str">
+          <cell r="O21" t="str">
             <v>MODEFENCE</v>
           </cell>
-          <cell r="C21">
-            <v>2406</v>
-          </cell>
-          <cell r="D21">
-            <v>90.08</v>
+          <cell r="P21">
+            <v>5036</v>
+          </cell>
+          <cell r="Q21">
+            <v>89.883312152501986</v>
           </cell>
         </row>
         <row r="22">
-          <cell r="B22" t="str">
+          <cell r="O22" t="str">
             <v>MON100</v>
           </cell>
-          <cell r="C22">
-            <v>105</v>
-          </cell>
-          <cell r="D22">
-            <v>222.69</v>
+          <cell r="P22">
+            <v>265</v>
+          </cell>
+          <cell r="Q22">
+            <v>222.87864150943395</v>
           </cell>
         </row>
         <row r="23">
-          <cell r="B23" t="str">
+          <cell r="O23" t="str">
             <v>MONIFTY500</v>
           </cell>
-          <cell r="C23">
-            <v>1221</v>
-          </cell>
-          <cell r="D23">
-            <v>23.35</v>
+          <cell r="P23">
+            <v>2524</v>
+          </cell>
+          <cell r="Q23">
+            <v>23.351786846275754</v>
           </cell>
         </row>
         <row r="24">
-          <cell r="B24" t="str">
+          <cell r="O24" t="str">
             <v>MOREALTY</v>
           </cell>
-          <cell r="C24">
-            <v>310</v>
-          </cell>
-          <cell r="D24">
-            <v>76.59</v>
+          <cell r="P24">
+            <v>713</v>
+          </cell>
+          <cell r="Q24">
+            <v>76.685750350631125</v>
           </cell>
         </row>
         <row r="25">
-          <cell r="B25" t="str">
+          <cell r="O25" t="str">
             <v>MOSMALL250</v>
           </cell>
-          <cell r="C25">
-            <v>1505</v>
-          </cell>
-          <cell r="D25">
-            <v>15.66</v>
+          <cell r="P25">
+            <v>3486</v>
+          </cell>
+          <cell r="Q25">
+            <v>15.663479632816982</v>
           </cell>
         </row>
         <row r="26">
-          <cell r="B26" t="str">
+          <cell r="O26" t="str">
             <v>NIFTYIETF</v>
           </cell>
-          <cell r="C26">
-            <v>80</v>
-          </cell>
-          <cell r="D26">
-            <v>279.52999999999997</v>
+          <cell r="P26">
+            <v>189</v>
+          </cell>
+          <cell r="Q26">
+            <v>280.08074074074074</v>
           </cell>
         </row>
         <row r="27">
-          <cell r="B27" t="str">
+          <cell r="O27" t="str">
             <v>OILIETF</v>
           </cell>
-          <cell r="C27">
-            <v>4185</v>
-          </cell>
-          <cell r="D27">
-            <v>12.21</v>
+          <cell r="P27">
+            <v>11764</v>
+          </cell>
+          <cell r="Q27">
+            <v>12.192873172390343</v>
           </cell>
         </row>
         <row r="28">
-          <cell r="B28" t="str">
+          <cell r="O28" t="str">
             <v>PSUBNKIETF</v>
           </cell>
-          <cell r="C28">
-            <v>1070</v>
-          </cell>
-          <cell r="D28">
-            <v>97.4</v>
+          <cell r="P28">
+            <v>2850</v>
+          </cell>
+          <cell r="Q28">
+            <v>97.531333333333336</v>
           </cell>
         </row>
         <row r="29">
-          <cell r="B29" t="str">
+          <cell r="O29" t="str">
             <v>PVTBANIETF</v>
           </cell>
-          <cell r="C29">
-            <v>3735</v>
-          </cell>
-          <cell r="D29">
-            <v>28.51</v>
+          <cell r="P29">
+            <v>7870</v>
+          </cell>
+          <cell r="Q29">
+            <v>28.546898348157558</v>
           </cell>
         </row>
         <row r="30">
-          <cell r="B30" t="str">
+          <cell r="O30" t="str">
             <v>SENSEXIETF</v>
           </cell>
-          <cell r="C30">
-            <v>25</v>
-          </cell>
-          <cell r="D30">
-            <v>915.24</v>
+          <cell r="P30">
+            <v>55</v>
+          </cell>
+          <cell r="Q30">
+            <v>916.2399999999999</v>
           </cell>
         </row>
         <row r="31">
-          <cell r="B31" t="str">
+          <cell r="O31" t="str">
             <v>TNIDETF</v>
           </cell>
-          <cell r="C31">
-            <v>290</v>
-          </cell>
-          <cell r="D31">
-            <v>80.83</v>
+          <cell r="P31">
+            <v>665</v>
+          </cell>
+          <cell r="Q31">
+            <v>80.906947368421058</v>
           </cell>
         </row>
       </sheetData>
@@ -1807,12 +1808,12 @@
         <v>6</v>
       </c>
       <c r="D2" s="5">
-        <f>LOOKUP(C2,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
-        <v>4290</v>
-      </c>
-      <c r="E2" s="5">
-        <f>LOOKUP(C2,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
-        <v>28.26</v>
+        <f>LOOKUP(C2,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
+        <v>7871</v>
+      </c>
+      <c r="E2" s="6">
+        <f>LOOKUP(C2,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
+        <v>28.303807648329308</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1826,12 +1827,12 @@
         <v>8</v>
       </c>
       <c r="D3" s="5">
-        <f>LOOKUP(C3,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
-        <v>1622</v>
-      </c>
-      <c r="E3" s="5">
-        <f>LOOKUP(C3,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
-        <v>99.99</v>
+        <f>LOOKUP(C3,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
+        <v>3365</v>
+      </c>
+      <c r="E3" s="6">
+        <f>LOOKUP(C3,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
+        <v>100.12240118870729</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1845,12 +1846,12 @@
         <v>10</v>
       </c>
       <c r="D4" s="5">
-        <f>LOOKUP(C4,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
-        <v>200</v>
-      </c>
-      <c r="E4" s="5">
-        <f>LOOKUP(C4,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
-        <v>117.18</v>
+        <f>LOOKUP(C4,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
+        <v>493</v>
+      </c>
+      <c r="E4" s="6">
+        <f>LOOKUP(C4,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
+        <v>117.38000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1864,12 +1865,12 @@
         <v>12</v>
       </c>
       <c r="D5" s="5">
-        <f>LOOKUP(C5,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
-        <v>2006</v>
-      </c>
-      <c r="E5" s="5">
-        <f>LOOKUP(C5,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
-        <v>102.29</v>
+        <f>LOOKUP(C5,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
+        <v>4215</v>
+      </c>
+      <c r="E5" s="6">
+        <f>LOOKUP(C5,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
+        <v>102.29550415183868</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1883,12 +1884,12 @@
         <v>14</v>
       </c>
       <c r="D6" s="5">
-        <f>LOOKUP(C6,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
-        <v>3620</v>
-      </c>
-      <c r="E6" s="5">
-        <f>LOOKUP(C6,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
-        <v>23.87</v>
+        <f>LOOKUP(C6,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
+        <v>8163</v>
+      </c>
+      <c r="E6" s="6">
+        <f>LOOKUP(C6,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
+        <v>23.879163297807182</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1902,12 +1903,12 @@
         <v>16</v>
       </c>
       <c r="D7" s="5">
-        <f>LOOKUP(C7,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
-        <v>2160</v>
-      </c>
-      <c r="E7" s="5">
-        <f>LOOKUP(C7,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
-        <v>30.23</v>
+        <f>LOOKUP(C7,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
+        <v>4522</v>
+      </c>
+      <c r="E7" s="6">
+        <f>LOOKUP(C7,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
+        <v>30.268575851393187</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1921,12 +1922,12 @@
         <v>18</v>
       </c>
       <c r="D8" s="5">
-        <f>LOOKUP(C8,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
-        <v>2695</v>
-      </c>
-      <c r="E8" s="5">
-        <f>LOOKUP(C8,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
-        <v>31.6</v>
+        <f>LOOKUP(C8,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
+        <v>5529</v>
+      </c>
+      <c r="E8" s="6">
+        <f>LOOKUP(C8,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
+        <v>31.559750406945195</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1940,12 +1941,12 @@
         <v>20</v>
       </c>
       <c r="D9" s="5">
-        <f>LOOKUP(C9,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
-        <v>435</v>
-      </c>
-      <c r="E9" s="5">
-        <f>LOOKUP(C9,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
-        <v>54.2</v>
+        <f>LOOKUP(C9,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
+        <v>1245</v>
+      </c>
+      <c r="E9" s="6">
+        <f>LOOKUP(C9,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
+        <v>54.28053012048192</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1959,12 +1960,12 @@
         <v>22</v>
       </c>
       <c r="D10" s="5">
-        <f>LOOKUP(C10,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
-        <v>1392</v>
-      </c>
-      <c r="E10" s="5">
-        <f>LOOKUP(C10,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
-        <v>151.41</v>
+        <f>LOOKUP(C10,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
+        <v>3196</v>
+      </c>
+      <c r="E10" s="6">
+        <f>LOOKUP(C10,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
+        <v>151.8827158948686</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1978,12 +1979,12 @@
         <v>24</v>
       </c>
       <c r="D11" s="5">
-        <f>LOOKUP(C11,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
-        <v>690</v>
-      </c>
-      <c r="E11" s="5">
-        <f>LOOKUP(C11,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
-        <v>95.75</v>
+        <f>LOOKUP(C11,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
+        <v>2625</v>
+      </c>
+      <c r="E11" s="6">
+        <f>LOOKUP(C11,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
+        <v>95.847759999999994</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1997,12 +1998,12 @@
         <v>26</v>
       </c>
       <c r="D12" s="5">
-        <f>LOOKUP(C12,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
-        <v>705</v>
-      </c>
-      <c r="E12" s="5">
-        <f>LOOKUP(C12,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
-        <v>33.369999999999997</v>
+        <f>LOOKUP(C12,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
+        <v>1687</v>
+      </c>
+      <c r="E12" s="6">
+        <f>LOOKUP(C12,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
+        <v>33.43657972732661</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2016,12 +2017,12 @@
         <v>28</v>
       </c>
       <c r="D13" s="5">
-        <f>LOOKUP(C13,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
-        <v>1135</v>
-      </c>
-      <c r="E13" s="5">
-        <f>LOOKUP(C13,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
-        <v>157.82</v>
+        <f>LOOKUP(C13,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
+        <v>2111</v>
+      </c>
+      <c r="E13" s="6">
+        <f>LOOKUP(C13,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
+        <v>158.05747513027003</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2035,12 +2036,12 @@
         <v>30</v>
       </c>
       <c r="D14" s="5">
-        <f>LOOKUP(C14,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
-        <v>700</v>
-      </c>
-      <c r="E14" s="5">
-        <f>LOOKUP(C14,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
-        <v>70.16</v>
+        <f>LOOKUP(C14,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
+        <v>3733</v>
+      </c>
+      <c r="E14" s="6">
+        <f>LOOKUP(C14,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
+        <v>69.903037771229577</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2054,12 +2055,12 @@
         <v>32</v>
       </c>
       <c r="D15" s="5">
-        <f>LOOKUP(C15,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
-        <v>9635</v>
-      </c>
-      <c r="E15" s="5">
-        <f>LOOKUP(C15,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
-        <v>12.24</v>
+        <f>LOOKUP(C15,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
+        <v>22981</v>
+      </c>
+      <c r="E15" s="6">
+        <f>LOOKUP(C15,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
+        <v>12.271476001914625</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2073,12 +2074,12 @@
         <v>34</v>
       </c>
       <c r="D16" s="5">
-        <f>LOOKUP(C16,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
-        <v>2605</v>
-      </c>
-      <c r="E16" s="5">
-        <f>LOOKUP(C16,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
-        <v>22.23</v>
+        <f>LOOKUP(C16,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
+        <v>5155</v>
+      </c>
+      <c r="E16" s="6">
+        <f>LOOKUP(C16,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
+        <v>22.226459747817653</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2092,12 +2093,12 @@
         <v>36</v>
       </c>
       <c r="D17" s="5">
-        <f>LOOKUP(C17,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
-        <v>7075</v>
-      </c>
-      <c r="E17" s="5">
-        <f>LOOKUP(C17,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
-        <v>32.11</v>
+        <f>LOOKUP(C17,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
+        <v>11452</v>
+      </c>
+      <c r="E17" s="6">
+        <f>LOOKUP(C17,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
+        <v>32.156601466992662</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2111,12 +2112,12 @@
         <v>38</v>
       </c>
       <c r="D18" s="5">
-        <f>LOOKUP(C18,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
-        <v>2406</v>
-      </c>
-      <c r="E18" s="5">
-        <f>LOOKUP(C18,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
-        <v>90.08</v>
+        <f>LOOKUP(C18,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
+        <v>5036</v>
+      </c>
+      <c r="E18" s="6">
+        <f>LOOKUP(C18,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
+        <v>89.883312152501986</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2130,12 +2131,12 @@
         <v>40</v>
       </c>
       <c r="D19" s="5">
-        <f>LOOKUP(C19,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
-        <v>105</v>
-      </c>
-      <c r="E19" s="5">
-        <f>LOOKUP(C19,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
-        <v>222.69</v>
+        <f>LOOKUP(C19,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
+        <v>265</v>
+      </c>
+      <c r="E19" s="6">
+        <f>LOOKUP(C19,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
+        <v>222.87864150943395</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2149,12 +2150,12 @@
         <v>42</v>
       </c>
       <c r="D20" s="5">
-        <f>LOOKUP(C20,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
-        <v>1221</v>
-      </c>
-      <c r="E20" s="5">
-        <f>LOOKUP(C20,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
-        <v>23.35</v>
+        <f>LOOKUP(C20,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
+        <v>2524</v>
+      </c>
+      <c r="E20" s="6">
+        <f>LOOKUP(C20,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
+        <v>23.351786846275754</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2168,12 +2169,12 @@
         <v>44</v>
       </c>
       <c r="D21" s="5">
-        <f>LOOKUP(C21,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
-        <v>310</v>
-      </c>
-      <c r="E21" s="5">
-        <f>LOOKUP(C21,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
-        <v>76.59</v>
+        <f>LOOKUP(C21,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
+        <v>713</v>
+      </c>
+      <c r="E21" s="6">
+        <f>LOOKUP(C21,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
+        <v>76.685750350631125</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2187,12 +2188,12 @@
         <v>46</v>
       </c>
       <c r="D22" s="5">
-        <f>LOOKUP(C22,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
-        <v>1505</v>
-      </c>
-      <c r="E22" s="5">
-        <f>LOOKUP(C22,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
-        <v>15.66</v>
+        <f>LOOKUP(C22,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
+        <v>3486</v>
+      </c>
+      <c r="E22" s="6">
+        <f>LOOKUP(C22,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
+        <v>15.663479632816982</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2206,12 +2207,12 @@
         <v>48</v>
       </c>
       <c r="D23" s="5">
-        <f>LOOKUP(C23,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
-        <v>80</v>
-      </c>
-      <c r="E23" s="5">
-        <f>LOOKUP(C23,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
-        <v>279.52999999999997</v>
+        <f>LOOKUP(C23,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
+        <v>189</v>
+      </c>
+      <c r="E23" s="6">
+        <f>LOOKUP(C23,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
+        <v>280.08074074074074</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2225,12 +2226,12 @@
         <v>50</v>
       </c>
       <c r="D24" s="5">
-        <f>LOOKUP(C24,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
-        <v>4185</v>
-      </c>
-      <c r="E24" s="5">
-        <f>LOOKUP(C24,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
-        <v>12.21</v>
+        <f>LOOKUP(C24,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
+        <v>11764</v>
+      </c>
+      <c r="E24" s="6">
+        <f>LOOKUP(C24,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
+        <v>12.192873172390343</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2244,12 +2245,12 @@
         <v>52</v>
       </c>
       <c r="D25" s="5">
-        <f>LOOKUP(C25,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
-        <v>1070</v>
-      </c>
-      <c r="E25" s="5">
-        <f>LOOKUP(C25,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
-        <v>97.4</v>
+        <f>LOOKUP(C25,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
+        <v>2850</v>
+      </c>
+      <c r="E25" s="6">
+        <f>LOOKUP(C25,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
+        <v>97.531333333333336</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2263,12 +2264,12 @@
         <v>54</v>
       </c>
       <c r="D26" s="5">
-        <f>LOOKUP(C26,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
-        <v>3735</v>
-      </c>
-      <c r="E26" s="5">
-        <f>LOOKUP(C26,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
-        <v>28.51</v>
+        <f>LOOKUP(C26,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
+        <v>7870</v>
+      </c>
+      <c r="E26" s="6">
+        <f>LOOKUP(C26,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
+        <v>28.546898348157558</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2282,12 +2283,12 @@
         <v>56</v>
       </c>
       <c r="D27" s="5">
-        <f>LOOKUP(C27,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
-        <v>290</v>
-      </c>
-      <c r="E27" s="5">
-        <f>LOOKUP(C27,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
-        <v>80.83</v>
+        <f>LOOKUP(C27,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
+        <v>665</v>
+      </c>
+      <c r="E27" s="6">
+        <f>LOOKUP(C27,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
+        <v>80.906947368421058</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2301,12 +2302,12 @@
         <v>57</v>
       </c>
       <c r="D28" s="5">
-        <f>LOOKUP(C28,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
-        <v>10530</v>
-      </c>
-      <c r="E28" s="5">
-        <f>LOOKUP(C28,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
-        <v>10.38</v>
+        <f>LOOKUP(C28,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
+        <v>21269</v>
+      </c>
+      <c r="E28" s="6">
+        <f>LOOKUP(C28,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
+        <v>10.362358361935209</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2320,17 +2321,17 @@
         <v>58</v>
       </c>
       <c r="D29" s="5">
-        <f>LOOKUP(C29,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
-        <v>1552</v>
-      </c>
-      <c r="E29" s="5">
-        <f>LOOKUP(C29,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
-        <v>27.6</v>
+        <f>LOOKUP(C29,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
+        <v>3172</v>
+      </c>
+      <c r="E29" s="6">
+        <f>LOOKUP(C29,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
+        <v>27.530201765447668</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>60</v>
@@ -2339,17 +2340,17 @@
         <v>62</v>
       </c>
       <c r="D30" s="5">
-        <f>LOOKUP(C30,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
-        <v>25</v>
-      </c>
-      <c r="E30" s="5">
-        <f>LOOKUP(C30,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
-        <v>915.24</v>
+        <f>LOOKUP(C30,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
+        <v>55</v>
+      </c>
+      <c r="E30" s="6">
+        <f>LOOKUP(C30,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
+        <v>916.2399999999999</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>60</v>
@@ -2358,12 +2359,12 @@
         <v>61</v>
       </c>
       <c r="D31" s="5">
-        <f>LOOKUP(C31,[1]positions!$B$2:$B$31,[1]positions!$C$2:$C$31)</f>
-        <v>2404</v>
-      </c>
-      <c r="E31" s="5">
-        <f>LOOKUP(C31,[1]positions!$B$2:$B$31,[1]positions!$D$2:$D$31)</f>
-        <v>61.29</v>
+        <f>LOOKUP(C31,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
+        <v>4804</v>
+      </c>
+      <c r="E31" s="6">
+        <f>LOOKUP(C31,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
+        <v>61.289999999999992</v>
       </c>
     </row>
   </sheetData>

--- a/ETF Summary Report.xlsx
+++ b/ETF Summary Report.xlsx
@@ -8,16 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manthan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0C49126-971E-B74D-B57C-533E6988AF41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDFC0910-C4C3-CD44-BDC4-81B781613FE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Manthan" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -376,353 +373,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="positions"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="O2" t="str">
-            <v>AUTOIETF</v>
-          </cell>
-          <cell r="P2">
-            <v>7871</v>
-          </cell>
-          <cell r="Q2">
-            <v>28.303807648329308</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="O3" t="str">
-            <v>BANKIETF</v>
-          </cell>
-          <cell r="P3">
-            <v>4804</v>
-          </cell>
-          <cell r="Q3">
-            <v>61.289999999999992</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="O4" t="str">
-            <v>CHEMICAL</v>
-          </cell>
-          <cell r="P4">
-            <v>3172</v>
-          </cell>
-          <cell r="Q4">
-            <v>27.530201765447668</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="O5" t="str">
-            <v>COMMOIETF</v>
-          </cell>
-          <cell r="P5">
-            <v>3365</v>
-          </cell>
-          <cell r="Q5">
-            <v>100.12240118870729</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="O6" t="str">
-            <v>CONSUMIETF</v>
-          </cell>
-          <cell r="P6">
-            <v>493</v>
-          </cell>
-          <cell r="Q6">
-            <v>117.38000000000001</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="O7" t="str">
-            <v>CPSEETF</v>
-          </cell>
-          <cell r="P7">
-            <v>4215</v>
-          </cell>
-          <cell r="Q7">
-            <v>102.29550415183868</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="O8" t="str">
-            <v>ECAPINSURE</v>
-          </cell>
-          <cell r="P8">
-            <v>8163</v>
-          </cell>
-          <cell r="Q8">
-            <v>23.879163297807182</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="O9" t="str">
-            <v>EVINDIA</v>
-          </cell>
-          <cell r="P9">
-            <v>4522</v>
-          </cell>
-          <cell r="Q9">
-            <v>30.268575851393187</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="O10" t="str">
-            <v>FINIETF</v>
-          </cell>
-          <cell r="P10">
-            <v>5529</v>
-          </cell>
-          <cell r="Q10">
-            <v>31.559750406945195</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="O11" t="str">
-            <v>FMCGIETF</v>
-          </cell>
-          <cell r="P11">
-            <v>1245</v>
-          </cell>
-          <cell r="Q11">
-            <v>54.28053012048192</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="O12" t="str">
-            <v>GROWWPOWER</v>
-          </cell>
-          <cell r="P12">
-            <v>21269</v>
-          </cell>
-          <cell r="Q12">
-            <v>10.362358361935209</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="O13" t="str">
-            <v>HEALTHIETF</v>
-          </cell>
-          <cell r="P13">
-            <v>3196</v>
-          </cell>
-          <cell r="Q13">
-            <v>151.8827158948686</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="O14" t="str">
-            <v>INFRAIETF</v>
-          </cell>
-          <cell r="P14">
-            <v>2625</v>
-          </cell>
-          <cell r="Q14">
-            <v>95.847759999999994</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="O15" t="str">
-            <v>ITIETF</v>
-          </cell>
-          <cell r="P15">
-            <v>1687</v>
-          </cell>
-          <cell r="Q15">
-            <v>33.43657972732661</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="O16" t="str">
-            <v>MAKEINDIA</v>
-          </cell>
-          <cell r="P16">
-            <v>2111</v>
-          </cell>
-          <cell r="Q16">
-            <v>158.05747513027003</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="O17" t="str">
-            <v>MASPTOP50</v>
-          </cell>
-          <cell r="P17">
-            <v>3733</v>
-          </cell>
-          <cell r="Q17">
-            <v>69.903037771229577</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="O18" t="str">
-            <v>METALIETF</v>
-          </cell>
-          <cell r="P18">
-            <v>22981</v>
-          </cell>
-          <cell r="Q18">
-            <v>12.271476001914625</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="O19" t="str">
-            <v>MIDCAPIETF</v>
-          </cell>
-          <cell r="P19">
-            <v>5155</v>
-          </cell>
-          <cell r="Q19">
-            <v>22.226459747817653</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="O20" t="str">
-            <v>MNC</v>
-          </cell>
-          <cell r="P20">
-            <v>11452</v>
-          </cell>
-          <cell r="Q20">
-            <v>32.156601466992662</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="O21" t="str">
-            <v>MODEFENCE</v>
-          </cell>
-          <cell r="P21">
-            <v>5036</v>
-          </cell>
-          <cell r="Q21">
-            <v>89.883312152501986</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="O22" t="str">
-            <v>MON100</v>
-          </cell>
-          <cell r="P22">
-            <v>265</v>
-          </cell>
-          <cell r="Q22">
-            <v>222.87864150943395</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="O23" t="str">
-            <v>MONIFTY500</v>
-          </cell>
-          <cell r="P23">
-            <v>2524</v>
-          </cell>
-          <cell r="Q23">
-            <v>23.351786846275754</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="O24" t="str">
-            <v>MOREALTY</v>
-          </cell>
-          <cell r="P24">
-            <v>713</v>
-          </cell>
-          <cell r="Q24">
-            <v>76.685750350631125</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="O25" t="str">
-            <v>MOSMALL250</v>
-          </cell>
-          <cell r="P25">
-            <v>3486</v>
-          </cell>
-          <cell r="Q25">
-            <v>15.663479632816982</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="O26" t="str">
-            <v>NIFTYIETF</v>
-          </cell>
-          <cell r="P26">
-            <v>189</v>
-          </cell>
-          <cell r="Q26">
-            <v>280.08074074074074</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="O27" t="str">
-            <v>OILIETF</v>
-          </cell>
-          <cell r="P27">
-            <v>11764</v>
-          </cell>
-          <cell r="Q27">
-            <v>12.192873172390343</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="O28" t="str">
-            <v>PSUBNKIETF</v>
-          </cell>
-          <cell r="P28">
-            <v>2850</v>
-          </cell>
-          <cell r="Q28">
-            <v>97.531333333333336</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="O29" t="str">
-            <v>PVTBANIETF</v>
-          </cell>
-          <cell r="P29">
-            <v>7870</v>
-          </cell>
-          <cell r="Q29">
-            <v>28.546898348157558</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="O30" t="str">
-            <v>SENSEXIETF</v>
-          </cell>
-          <cell r="P30">
-            <v>55</v>
-          </cell>
-          <cell r="Q30">
-            <v>916.2399999999999</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="O31" t="str">
-            <v>TNIDETF</v>
-          </cell>
-          <cell r="P31">
-            <v>665</v>
-          </cell>
-          <cell r="Q31">
-            <v>80.906947368421058</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1808,12 +1458,10 @@
         <v>6</v>
       </c>
       <c r="D2" s="5">
-        <f>LOOKUP(C2,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
-        <v>7871</v>
+        <v>9017</v>
       </c>
       <c r="E2" s="6">
-        <f>LOOKUP(C2,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
-        <v>28.303807648329308</v>
+        <v>28.22</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1827,12 +1475,10 @@
         <v>8</v>
       </c>
       <c r="D3" s="5">
-        <f>LOOKUP(C3,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
-        <v>3365</v>
+        <v>4175</v>
       </c>
       <c r="E3" s="6">
-        <f>LOOKUP(C3,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
-        <v>100.12240118870729</v>
+        <v>99.66</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1846,12 +1492,10 @@
         <v>10</v>
       </c>
       <c r="D4" s="5">
-        <f>LOOKUP(C4,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
-        <v>493</v>
+        <v>585</v>
       </c>
       <c r="E4" s="6">
-        <f>LOOKUP(C4,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
-        <v>117.38000000000001</v>
+        <v>117.08</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1865,12 +1509,10 @@
         <v>12</v>
       </c>
       <c r="D5" s="5">
-        <f>LOOKUP(C5,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
-        <v>4215</v>
+        <v>5217</v>
       </c>
       <c r="E5" s="6">
-        <f>LOOKUP(C5,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
-        <v>102.29550415183868</v>
+        <v>102.16</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1884,12 +1526,10 @@
         <v>14</v>
       </c>
       <c r="D6" s="5">
-        <f>LOOKUP(C6,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
-        <v>8163</v>
+        <v>9649</v>
       </c>
       <c r="E6" s="6">
-        <f>LOOKUP(C6,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
-        <v>23.879163297807182</v>
+        <v>23.81</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1903,12 +1543,10 @@
         <v>16</v>
       </c>
       <c r="D7" s="5">
-        <f>LOOKUP(C7,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
-        <v>4522</v>
+        <v>5272</v>
       </c>
       <c r="E7" s="6">
-        <f>LOOKUP(C7,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
-        <v>30.268575851393187</v>
+        <v>30.17</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1922,12 +1560,10 @@
         <v>18</v>
       </c>
       <c r="D8" s="5">
-        <f>LOOKUP(C8,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
-        <v>5529</v>
+        <v>6876</v>
       </c>
       <c r="E8" s="6">
-        <f>LOOKUP(C8,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
-        <v>31.559750406945195</v>
+        <v>31.39</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1941,12 +1577,10 @@
         <v>20</v>
       </c>
       <c r="D9" s="5">
-        <f>LOOKUP(C9,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
-        <v>1245</v>
+        <v>1503</v>
       </c>
       <c r="E9" s="6">
-        <f>LOOKUP(C9,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
-        <v>54.28053012048192</v>
+        <v>54.14</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1960,12 +1594,10 @@
         <v>22</v>
       </c>
       <c r="D10" s="5">
-        <f>LOOKUP(C10,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
-        <v>3196</v>
+        <v>4090</v>
       </c>
       <c r="E10" s="6">
-        <f>LOOKUP(C10,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
-        <v>151.8827158948686</v>
+        <v>151.6</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1979,12 +1611,10 @@
         <v>24</v>
       </c>
       <c r="D11" s="5">
-        <f>LOOKUP(C11,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
-        <v>2625</v>
+        <v>3263</v>
       </c>
       <c r="E11" s="6">
-        <f>LOOKUP(C11,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
-        <v>95.847759999999994</v>
+        <v>95.4</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1998,12 +1628,10 @@
         <v>26</v>
       </c>
       <c r="D12" s="5">
-        <f>LOOKUP(C12,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
-        <v>1687</v>
+        <v>1975</v>
       </c>
       <c r="E12" s="6">
-        <f>LOOKUP(C12,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
-        <v>33.43657972732661</v>
+        <v>33.450000000000003</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2017,12 +1645,10 @@
         <v>28</v>
       </c>
       <c r="D13" s="5">
-        <f>LOOKUP(C13,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
-        <v>2111</v>
+        <v>2393</v>
       </c>
       <c r="E13" s="6">
-        <f>LOOKUP(C13,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
-        <v>158.05747513027003</v>
+        <v>157.66999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2036,12 +1662,10 @@
         <v>30</v>
       </c>
       <c r="D14" s="5">
-        <f>LOOKUP(C14,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
-        <v>3733</v>
+        <v>4737</v>
       </c>
       <c r="E14" s="6">
-        <f>LOOKUP(C14,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
-        <v>69.903037771229577</v>
+        <v>69.77</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2055,12 +1679,10 @@
         <v>32</v>
       </c>
       <c r="D15" s="5">
-        <f>LOOKUP(C15,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
-        <v>22981</v>
+        <v>27147</v>
       </c>
       <c r="E15" s="6">
-        <f>LOOKUP(C15,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
-        <v>12.271476001914625</v>
+        <v>12.22</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2074,12 +1696,10 @@
         <v>34</v>
       </c>
       <c r="D16" s="5">
-        <f>LOOKUP(C16,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
-        <v>5155</v>
+        <v>5975</v>
       </c>
       <c r="E16" s="6">
-        <f>LOOKUP(C16,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
-        <v>22.226459747817653</v>
+        <v>22.16</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2093,12 +1713,10 @@
         <v>36</v>
       </c>
       <c r="D17" s="5">
-        <f>LOOKUP(C17,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
-        <v>11452</v>
+        <v>12866</v>
       </c>
       <c r="E17" s="6">
-        <f>LOOKUP(C17,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
-        <v>32.156601466992662</v>
+        <v>32.08</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2112,12 +1730,10 @@
         <v>38</v>
       </c>
       <c r="D18" s="5">
-        <f>LOOKUP(C18,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
-        <v>5036</v>
+        <v>6239</v>
       </c>
       <c r="E18" s="6">
-        <f>LOOKUP(C18,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
-        <v>89.883312152501986</v>
+        <v>89.75</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2131,12 +1747,10 @@
         <v>40</v>
       </c>
       <c r="D19" s="5">
-        <f>LOOKUP(C19,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
-        <v>265</v>
+        <v>307</v>
       </c>
       <c r="E19" s="6">
-        <f>LOOKUP(C19,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
-        <v>222.87864150943395</v>
+        <v>222.42</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2150,12 +1764,10 @@
         <v>42</v>
       </c>
       <c r="D20" s="5">
-        <f>LOOKUP(C20,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
-        <v>2524</v>
+        <v>3133</v>
       </c>
       <c r="E20" s="6">
-        <f>LOOKUP(C20,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
-        <v>23.351786846275754</v>
+        <v>23.26</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2169,12 +1781,10 @@
         <v>44</v>
       </c>
       <c r="D21" s="5">
-        <f>LOOKUP(C21,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
-        <v>713</v>
+        <v>839</v>
       </c>
       <c r="E21" s="6">
-        <f>LOOKUP(C21,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
-        <v>76.685750350631125</v>
+        <v>76.400000000000006</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2188,12 +1798,10 @@
         <v>46</v>
       </c>
       <c r="D22" s="5">
-        <f>LOOKUP(C22,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
-        <v>3486</v>
+        <v>4104</v>
       </c>
       <c r="E22" s="6">
-        <f>LOOKUP(C22,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
-        <v>15.663479632816982</v>
+        <v>15.62</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2207,12 +1815,10 @@
         <v>48</v>
       </c>
       <c r="D23" s="5">
-        <f>LOOKUP(C23,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
-        <v>189</v>
+        <v>257</v>
       </c>
       <c r="E23" s="6">
-        <f>LOOKUP(C23,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
-        <v>280.08074074074074</v>
+        <v>278.91000000000003</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2226,12 +1832,10 @@
         <v>50</v>
       </c>
       <c r="D24" s="5">
-        <f>LOOKUP(C24,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
-        <v>11764</v>
+        <v>14234</v>
       </c>
       <c r="E24" s="6">
-        <f>LOOKUP(C24,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
-        <v>12.192873172390343</v>
+        <v>12.14</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2245,12 +1849,10 @@
         <v>52</v>
       </c>
       <c r="D25" s="5">
-        <f>LOOKUP(C25,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
-        <v>2850</v>
+        <v>3370</v>
       </c>
       <c r="E25" s="6">
-        <f>LOOKUP(C25,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
-        <v>97.531333333333336</v>
+        <v>97.14</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2264,12 +1866,10 @@
         <v>54</v>
       </c>
       <c r="D26" s="5">
-        <f>LOOKUP(C26,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
-        <v>7870</v>
+        <v>9736</v>
       </c>
       <c r="E26" s="6">
-        <f>LOOKUP(C26,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
-        <v>28.546898348157558</v>
+        <v>28.47</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2283,12 +1883,10 @@
         <v>56</v>
       </c>
       <c r="D27" s="5">
-        <f>LOOKUP(C27,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
-        <v>665</v>
+        <v>783</v>
       </c>
       <c r="E27" s="6">
-        <f>LOOKUP(C27,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
-        <v>80.906947368421058</v>
+        <v>80.86</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2302,12 +1900,10 @@
         <v>57</v>
       </c>
       <c r="D28" s="5">
-        <f>LOOKUP(C28,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
-        <v>21269</v>
+        <v>26534</v>
       </c>
       <c r="E28" s="6">
-        <f>LOOKUP(C28,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
-        <v>10.362358361935209</v>
+        <v>10.32</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2321,12 +1917,10 @@
         <v>58</v>
       </c>
       <c r="D29" s="5">
-        <f>LOOKUP(C29,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
-        <v>3172</v>
+        <v>3946</v>
       </c>
       <c r="E29" s="6">
-        <f>LOOKUP(C29,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
-        <v>27.530201765447668</v>
+        <v>27.45</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2340,12 +1934,10 @@
         <v>62</v>
       </c>
       <c r="D30" s="5">
-        <f>LOOKUP(C30,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E30" s="6">
-        <f>LOOKUP(C30,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
-        <v>916.2399999999999</v>
+        <v>914.17</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2359,12 +1951,10 @@
         <v>61</v>
       </c>
       <c r="D31" s="5">
-        <f>LOOKUP(C31,[1]positions!$O$2:$O$31,[1]positions!$P$2:$P$31)</f>
-        <v>4804</v>
+        <v>6004</v>
       </c>
       <c r="E31" s="6">
-        <f>LOOKUP(C31,[1]positions!$O$2:$O$31,[1]positions!$Q$2:$Q$31)</f>
-        <v>61.289999999999992</v>
+        <v>61.09</v>
       </c>
     </row>
   </sheetData>

--- a/ETF Summary Report.xlsx
+++ b/ETF Summary Report.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manthan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDFC0910-C4C3-CD44-BDC4-81B781613FE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA82FD6B-1380-3140-A2EC-19A577DCCAC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Manthan" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -24,7 +24,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -1458,10 +1457,10 @@
         <v>6</v>
       </c>
       <c r="D2" s="5">
-        <v>9017</v>
+        <v>9066</v>
       </c>
       <c r="E2" s="6">
-        <v>28.22</v>
+        <v>28.21</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1475,7 +1474,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="5">
-        <v>4175</v>
+        <v>4194</v>
       </c>
       <c r="E3" s="6">
         <v>99.66</v>
@@ -1492,10 +1491,10 @@
         <v>10</v>
       </c>
       <c r="D4" s="5">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="E4" s="6">
-        <v>117.08</v>
+        <v>117.07</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1509,7 +1508,7 @@
         <v>12</v>
       </c>
       <c r="D5" s="5">
-        <v>5217</v>
+        <v>5221</v>
       </c>
       <c r="E5" s="6">
         <v>102.16</v>
@@ -1526,10 +1525,10 @@
         <v>14</v>
       </c>
       <c r="D6" s="5">
-        <v>9649</v>
+        <v>9859</v>
       </c>
       <c r="E6" s="6">
-        <v>23.81</v>
+        <v>23.79</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1543,10 +1542,10 @@
         <v>16</v>
       </c>
       <c r="D7" s="5">
-        <v>5272</v>
+        <v>5288</v>
       </c>
       <c r="E7" s="6">
-        <v>30.17</v>
+        <v>30.16</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1560,10 +1559,10 @@
         <v>18</v>
       </c>
       <c r="D8" s="5">
-        <v>6876</v>
+        <v>6941</v>
       </c>
       <c r="E8" s="6">
-        <v>31.39</v>
+        <v>31.38</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1577,7 +1576,7 @@
         <v>20</v>
       </c>
       <c r="D9" s="5">
-        <v>1503</v>
+        <v>1512</v>
       </c>
       <c r="E9" s="6">
         <v>54.14</v>
@@ -1594,7 +1593,7 @@
         <v>22</v>
       </c>
       <c r="D10" s="5">
-        <v>4090</v>
+        <v>4112</v>
       </c>
       <c r="E10" s="6">
         <v>151.6</v>
@@ -1611,7 +1610,7 @@
         <v>24</v>
       </c>
       <c r="D11" s="5">
-        <v>3263</v>
+        <v>3268</v>
       </c>
       <c r="E11" s="6">
         <v>95.4</v>
@@ -1628,7 +1627,7 @@
         <v>26</v>
       </c>
       <c r="D12" s="5">
-        <v>1975</v>
+        <v>1989</v>
       </c>
       <c r="E12" s="6">
         <v>33.450000000000003</v>
@@ -1645,7 +1644,7 @@
         <v>28</v>
       </c>
       <c r="D13" s="5">
-        <v>2393</v>
+        <v>2410</v>
       </c>
       <c r="E13" s="6">
         <v>157.66999999999999</v>
@@ -1662,10 +1661,10 @@
         <v>30</v>
       </c>
       <c r="D14" s="5">
-        <v>4737</v>
+        <v>4766</v>
       </c>
       <c r="E14" s="6">
-        <v>69.77</v>
+        <v>69.78</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1679,7 +1678,7 @@
         <v>32</v>
       </c>
       <c r="D15" s="5">
-        <v>27147</v>
+        <v>27277</v>
       </c>
       <c r="E15" s="6">
         <v>12.22</v>
@@ -1696,7 +1695,7 @@
         <v>34</v>
       </c>
       <c r="D16" s="5">
-        <v>5975</v>
+        <v>5997</v>
       </c>
       <c r="E16" s="6">
         <v>22.16</v>
@@ -1713,10 +1712,10 @@
         <v>36</v>
       </c>
       <c r="D17" s="5">
-        <v>12866</v>
+        <v>13020</v>
       </c>
       <c r="E17" s="6">
-        <v>32.08</v>
+        <v>32.07</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1730,10 +1729,10 @@
         <v>38</v>
       </c>
       <c r="D18" s="5">
-        <v>6239</v>
+        <v>6264</v>
       </c>
       <c r="E18" s="6">
-        <v>89.75</v>
+        <v>89.77</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1747,10 +1746,10 @@
         <v>40</v>
       </c>
       <c r="D19" s="5">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="E19" s="6">
-        <v>222.42</v>
+        <v>222.4</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1764,7 +1763,7 @@
         <v>42</v>
       </c>
       <c r="D20" s="5">
-        <v>3133</v>
+        <v>3205</v>
       </c>
       <c r="E20" s="6">
         <v>23.26</v>
@@ -1781,10 +1780,10 @@
         <v>44</v>
       </c>
       <c r="D21" s="5">
-        <v>839</v>
+        <v>845</v>
       </c>
       <c r="E21" s="6">
-        <v>76.400000000000006</v>
+        <v>76.39</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1798,7 +1797,7 @@
         <v>46</v>
       </c>
       <c r="D22" s="5">
-        <v>4104</v>
+        <v>4135</v>
       </c>
       <c r="E22" s="6">
         <v>15.62</v>
@@ -1815,10 +1814,10 @@
         <v>48</v>
       </c>
       <c r="D23" s="5">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E23" s="6">
-        <v>278.91000000000003</v>
+        <v>278.89999999999998</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1832,7 +1831,7 @@
         <v>50</v>
       </c>
       <c r="D24" s="5">
-        <v>14234</v>
+        <v>14274</v>
       </c>
       <c r="E24" s="6">
         <v>12.14</v>
@@ -1849,10 +1848,10 @@
         <v>52</v>
       </c>
       <c r="D25" s="5">
-        <v>3370</v>
+        <v>3416</v>
       </c>
       <c r="E25" s="6">
-        <v>97.14</v>
+        <v>97.09</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1866,10 +1865,10 @@
         <v>54</v>
       </c>
       <c r="D26" s="5">
-        <v>9736</v>
+        <v>9845</v>
       </c>
       <c r="E26" s="6">
-        <v>28.47</v>
+        <v>28.46</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1883,10 +1882,10 @@
         <v>56</v>
       </c>
       <c r="D27" s="5">
-        <v>783</v>
+        <v>789</v>
       </c>
       <c r="E27" s="6">
-        <v>80.86</v>
+        <v>80.849999999999994</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1900,7 +1899,7 @@
         <v>57</v>
       </c>
       <c r="D28" s="5">
-        <v>26534</v>
+        <v>26663</v>
       </c>
       <c r="E28" s="6">
         <v>10.32</v>
@@ -1917,7 +1916,7 @@
         <v>58</v>
       </c>
       <c r="D29" s="5">
-        <v>3946</v>
+        <v>3963</v>
       </c>
       <c r="E29" s="6">
         <v>27.45</v>
@@ -1934,10 +1933,10 @@
         <v>62</v>
       </c>
       <c r="D30" s="5">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E30" s="6">
-        <v>914.17</v>
+        <v>913.99</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1951,10 +1950,10 @@
         <v>61</v>
       </c>
       <c r="D31" s="5">
-        <v>6004</v>
+        <v>6064</v>
       </c>
       <c r="E31" s="6">
-        <v>61.09</v>
+        <v>61.07</v>
       </c>
     </row>
   </sheetData>

--- a/ETF Summary Report.xlsx
+++ b/ETF Summary Report.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manthan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA82FD6B-1380-3140-A2EC-19A577DCCAC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{199540A0-7110-744F-83E6-57322FAA720A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Manthan" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Manthan!$A$1:$E$1</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -32,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
   <si>
     <t>SR. NO.</t>
   </si>
@@ -49,178 +52,85 @@
     <t>AVERAGE PRICE</t>
   </si>
   <si>
-    <t>ICICI Prudential Nifty Auto ETF</t>
-  </si>
-  <si>
-    <t>AUTOIETF</t>
-  </si>
-  <si>
-    <t>ICICI Prudential Nifty Commodities ETF</t>
-  </si>
-  <si>
-    <t>COMMOIETF</t>
-  </si>
-  <si>
-    <t>ICICI Prudential Nifty Consumption ETF</t>
-  </si>
-  <si>
-    <t>CONSUMIETF</t>
-  </si>
-  <si>
-    <t>CPSE ETF</t>
-  </si>
-  <si>
-    <t>CPSEETF</t>
-  </si>
-  <si>
-    <t>Edelweiss BSE Capital Markets &amp; Insurance ETF</t>
-  </si>
-  <si>
-    <t>ECAPINSURE</t>
-  </si>
-  <si>
-    <t>Mirae Asset Nifty EV and New Age Automotive ETF</t>
-  </si>
-  <si>
-    <t>EVINDIA</t>
-  </si>
-  <si>
-    <t>ICICI Prudential Nifty Financial Serv. Ex-Bank ETF</t>
-  </si>
-  <si>
-    <t>FINIETF</t>
-  </si>
-  <si>
-    <t>ICICI Prudential Nifty FMCG ETF</t>
-  </si>
-  <si>
-    <t>FMCGIETF</t>
-  </si>
-  <si>
-    <t>ICICI Prudential Nifty Healthcare ETF</t>
-  </si>
-  <si>
-    <t>HEALTHIETF</t>
-  </si>
-  <si>
-    <t>ICICI Prudential Nifty Infrastructure ETF</t>
-  </si>
-  <si>
-    <t>INFRAIETF</t>
-  </si>
-  <si>
-    <t>ICICI Prudential Nifty IT ETF</t>
-  </si>
-  <si>
-    <t>ITIETF</t>
-  </si>
-  <si>
-    <t>Mirae Asset Nifty India Manufacturing ETF</t>
-  </si>
-  <si>
-    <t>MAKEINDIA</t>
-  </si>
-  <si>
-    <t>Mirae Asset S&amp;P 500 Top 50 ETF</t>
-  </si>
-  <si>
-    <t>MASPTOP50</t>
-  </si>
-  <si>
-    <t>ICICI Prudential Nifty Metal ETF</t>
-  </si>
-  <si>
-    <t>METALIETF</t>
-  </si>
-  <si>
-    <t>ICICI Prudential Nifty Midcap 150 ETF</t>
-  </si>
-  <si>
-    <t>MIDCAPIETF</t>
-  </si>
-  <si>
-    <t>Kotak Nifty MNC ETF</t>
-  </si>
-  <si>
-    <t>MNC</t>
-  </si>
-  <si>
-    <t>Motilal Oswal Nifty India Defence ETF</t>
-  </si>
-  <si>
-    <t>MODEFENCE</t>
-  </si>
-  <si>
-    <t>Motilal Oswal MOSt Shares NASDAQ-100 ETF</t>
-  </si>
-  <si>
-    <t>MON100</t>
-  </si>
-  <si>
-    <t>Motilal Oswal Nifty 500 ETF</t>
-  </si>
-  <si>
-    <t>MONIFTY500</t>
-  </si>
-  <si>
-    <t>Motilal Oswal Nifty Realty ETF</t>
-  </si>
-  <si>
-    <t>MOREALTY</t>
-  </si>
-  <si>
-    <t>Motilal Oswal Nifty Smallcap 250</t>
-  </si>
-  <si>
-    <t>MOSMALL250</t>
-  </si>
-  <si>
-    <t>ICICI Prudential Nifty 50 ETF</t>
-  </si>
-  <si>
-    <t>NIFTYIETF</t>
-  </si>
-  <si>
-    <t>ICICI Prudential Nifty Oil &amp; Gas ETF</t>
-  </si>
-  <si>
-    <t>OILIETF</t>
-  </si>
-  <si>
-    <t>ICICI Prudential Nifty PSU Bank ETF</t>
-  </si>
-  <si>
-    <t>PSUBNKIETF</t>
-  </si>
-  <si>
-    <t>ICICI Prudential Nifty Private Bank ETF</t>
-  </si>
-  <si>
-    <t>PVTBANIETF</t>
-  </si>
-  <si>
-    <t>Tata Nifty India Digital ETF</t>
-  </si>
-  <si>
-    <t>TNIDETF</t>
-  </si>
-  <si>
-    <t>GROWWPOWER</t>
-  </si>
-  <si>
-    <t>CHEMICAL</t>
-  </si>
-  <si>
-    <t>Groww BSE Power ETF</t>
-  </si>
-  <si>
-    <t>Kotak Nifty Chemicals ETF</t>
-  </si>
-  <si>
-    <t>BANKIETF</t>
-  </si>
-  <si>
-    <t>SENSEXIETF</t>
+    <t>AMBUJACEM</t>
+  </si>
+  <si>
+    <t>BALRAMCHIN</t>
+  </si>
+  <si>
+    <t>DWARKESH</t>
+  </si>
+  <si>
+    <t>EIDPARRY</t>
+  </si>
+  <si>
+    <t>INDUSTOWER</t>
+  </si>
+  <si>
+    <t>INFY</t>
+  </si>
+  <si>
+    <t>JUBLFOOD</t>
+  </si>
+  <si>
+    <t>KFINTECH</t>
+  </si>
+  <si>
+    <t>KOTAKBANK</t>
+  </si>
+  <si>
+    <t>PATANJALI</t>
+  </si>
+  <si>
+    <t>PFC</t>
+  </si>
+  <si>
+    <t>RENUKA</t>
+  </si>
+  <si>
+    <t>SBICARD</t>
+  </si>
+  <si>
+    <t>TATACONSUM</t>
+  </si>
+  <si>
+    <t>TRIVENI</t>
+  </si>
+  <si>
+    <t>AMBUJA CEMENT</t>
+  </si>
+  <si>
+    <t>BALRAMPUR CHINNI</t>
+  </si>
+  <si>
+    <t>DWARKESH SUGAR</t>
+  </si>
+  <si>
+    <t>EID PARRY</t>
+  </si>
+  <si>
+    <t>INDUS TOWER</t>
+  </si>
+  <si>
+    <t>INFOSYS</t>
+  </si>
+  <si>
+    <t>JUBILANT FOOODS</t>
+  </si>
+  <si>
+    <t>KOTAK BANK</t>
+  </si>
+  <si>
+    <t>RENUKA SUGAR</t>
+  </si>
+  <si>
+    <t>SBI CARDS</t>
+  </si>
+  <si>
+    <t>TATA CONSUMER</t>
+  </si>
+  <si>
+    <t>TRIVENI ENGINEERING</t>
   </si>
 </sst>
 </file>
@@ -281,14 +191,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1419,7 +1327,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="1" customWidth="1"/>
@@ -1451,16 +1359,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="5">
-        <v>9066</v>
-      </c>
-      <c r="E2" s="6">
-        <v>28.21</v>
+      <c r="D2">
+        <v>110</v>
+      </c>
+      <c r="E2">
+        <v>450.2</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1468,16 +1376,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="5">
-        <v>4194</v>
-      </c>
-      <c r="E3" s="6">
-        <v>99.66</v>
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3">
+        <v>190</v>
+      </c>
+      <c r="E3">
+        <v>519.33000000000004</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1485,16 +1393,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="5">
-        <v>589</v>
-      </c>
-      <c r="E4" s="6">
-        <v>117.07</v>
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4">
+        <v>2082</v>
+      </c>
+      <c r="E4">
+        <v>47.87</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1502,16 +1410,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="5">
-        <v>5221</v>
-      </c>
-      <c r="E5" s="6">
-        <v>102.16</v>
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5">
+        <v>118</v>
+      </c>
+      <c r="E5">
+        <v>836.01</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1519,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="5">
-        <v>9859</v>
-      </c>
-      <c r="E6" s="6">
-        <v>23.79</v>
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6">
+        <v>125</v>
+      </c>
+      <c r="E6">
+        <v>398.55</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1536,16 +1444,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="5">
-        <v>5288</v>
-      </c>
-      <c r="E7" s="6">
-        <v>30.16</v>
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7">
+        <v>42</v>
+      </c>
+      <c r="E7">
+        <v>1169.3</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1553,16 +1461,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="5">
-        <v>6941</v>
-      </c>
-      <c r="E8" s="6">
-        <v>31.38</v>
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8">
+        <v>104</v>
+      </c>
+      <c r="E8">
+        <v>477.57</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1570,16 +1478,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="5">
-        <v>1512</v>
-      </c>
-      <c r="E9" s="6">
-        <v>54.14</v>
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9">
+        <v>54</v>
+      </c>
+      <c r="E9">
+        <v>918.7</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1587,376 +1495,122 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="5">
-        <v>4112</v>
-      </c>
-      <c r="E10" s="6">
-        <v>151.6</v>
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10">
+        <v>132</v>
+      </c>
+      <c r="E10">
+        <v>378.1</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="5">
-        <v>3268</v>
-      </c>
-      <c r="E11" s="6">
-        <v>95.4</v>
+        <v>14</v>
+      </c>
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11">
+        <v>108</v>
+      </c>
+      <c r="E11">
+        <v>462</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" s="5">
-        <v>1989</v>
-      </c>
-      <c r="E12" s="6">
-        <v>33.450000000000003</v>
+        <v>15</v>
+      </c>
+      <c r="C12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12">
+        <v>107</v>
+      </c>
+      <c r="E12">
+        <v>464.65</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="5">
-        <v>2410</v>
-      </c>
-      <c r="E13" s="6">
-        <v>157.66999999999999</v>
+      <c r="C13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13">
+        <v>3602</v>
+      </c>
+      <c r="E13">
+        <v>27.73</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" s="5">
-        <v>4766</v>
-      </c>
-      <c r="E14" s="6">
-        <v>69.78</v>
+      <c r="C14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14">
+        <v>77</v>
+      </c>
+      <c r="E14">
+        <v>646.65</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" s="5">
-        <v>27277</v>
-      </c>
-      <c r="E15" s="6">
-        <v>12.22</v>
+        <v>30</v>
+      </c>
+      <c r="C15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15">
+        <v>42</v>
+      </c>
+      <c r="E15">
+        <v>1171.9000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D16" s="5">
-        <v>5997</v>
-      </c>
-      <c r="E16" s="6">
-        <v>22.16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="3">
-        <v>16</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D17" s="5">
-        <v>13020</v>
-      </c>
-      <c r="E17" s="6">
-        <v>32.07</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="3">
-        <v>17</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D18" s="5">
-        <v>6264</v>
-      </c>
-      <c r="E18" s="6">
-        <v>89.77</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="3">
-        <v>18</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D19" s="5">
-        <v>312</v>
-      </c>
-      <c r="E19" s="6">
-        <v>222.4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="3">
+        <v>31</v>
+      </c>
+      <c r="C16" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D20" s="5">
-        <v>3205</v>
-      </c>
-      <c r="E20" s="6">
-        <v>23.26</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="3">
-        <v>20</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D21" s="5">
-        <v>845</v>
-      </c>
-      <c r="E21" s="6">
-        <v>76.39</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="3">
-        <v>21</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D22" s="5">
-        <v>4135</v>
-      </c>
-      <c r="E22" s="6">
-        <v>15.62</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="3">
-        <v>22</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D23" s="5">
-        <v>258</v>
-      </c>
-      <c r="E23" s="6">
-        <v>278.89999999999998</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="3">
-        <v>23</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D24" s="5">
-        <v>14274</v>
-      </c>
-      <c r="E24" s="6">
-        <v>12.14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="3">
-        <v>24</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D25" s="5">
-        <v>3416</v>
-      </c>
-      <c r="E25" s="6">
-        <v>97.09</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="3">
-        <v>25</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D26" s="5">
-        <v>9845</v>
-      </c>
-      <c r="E26" s="6">
-        <v>28.46</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="3">
-        <v>26</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D27" s="5">
-        <v>789</v>
-      </c>
-      <c r="E27" s="6">
-        <v>80.849999999999994</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="3">
-        <v>27</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D28" s="5">
-        <v>26663</v>
-      </c>
-      <c r="E28" s="6">
-        <v>10.32</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="3">
-        <v>28</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D29" s="5">
-        <v>3963</v>
-      </c>
-      <c r="E29" s="6">
-        <v>27.45</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="3">
-        <v>29</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D30" s="5">
-        <v>66</v>
-      </c>
-      <c r="E30" s="6">
-        <v>913.99</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="3">
-        <v>30</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D31" s="5">
-        <v>6064</v>
-      </c>
-      <c r="E31" s="6">
-        <v>61.07</v>
+      <c r="D16">
+        <v>248</v>
+      </c>
+      <c r="E16">
+        <v>400.47</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <headerFooter>

--- a/ETF Summary Report.xlsx
+++ b/ETF Summary Report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manthan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{199540A0-7110-744F-83E6-57322FAA720A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D1A5D04-71DB-064C-B751-3884CBF7AE9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Manthan" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="40">
   <si>
     <t>SR. NO.</t>
   </si>
@@ -131,13 +131,37 @@
   </si>
   <si>
     <t>TRIVENI ENGINEERING</t>
+  </si>
+  <si>
+    <t>HCLTECH</t>
+  </si>
+  <si>
+    <t>INDIANB</t>
+  </si>
+  <si>
+    <t>LTM</t>
+  </si>
+  <si>
+    <t>MFSL</t>
+  </si>
+  <si>
+    <t>TECHM</t>
+  </si>
+  <si>
+    <t>HCLT TECHNOLOGIES</t>
+  </si>
+  <si>
+    <t>INDIAN BANK</t>
+  </si>
+  <si>
+    <t>TECH MAHINDRA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -154,6 +178,12 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -191,12 +221,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1327,7 +1361,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="1" customWidth="1"/>
@@ -1361,13 +1395,13 @@
       <c r="B2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="5">
         <v>110</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="5">
         <v>450.2</v>
       </c>
     </row>
@@ -1378,13 +1412,13 @@
       <c r="B3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="5">
         <v>190</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="5">
         <v>519.33000000000004</v>
       </c>
     </row>
@@ -1395,13 +1429,13 @@
       <c r="B4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="5">
         <v>2082</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="5">
         <v>47.87</v>
       </c>
     </row>
@@ -1412,13 +1446,13 @@
       <c r="B5" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="5">
         <v>118</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="5">
         <v>836.01</v>
       </c>
     </row>
@@ -1429,13 +1463,13 @@
       <c r="B6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="5">
         <v>125</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="5">
         <v>398.55</v>
       </c>
     </row>
@@ -1446,13 +1480,13 @@
       <c r="B7" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="5">
         <v>42</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="5">
         <v>1169.3</v>
       </c>
     </row>
@@ -1463,13 +1497,13 @@
       <c r="B8" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="5">
         <v>104</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="5">
         <v>477.57</v>
       </c>
     </row>
@@ -1480,13 +1514,13 @@
       <c r="B9" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="5">
         <v>54</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="5">
         <v>918.7</v>
       </c>
     </row>
@@ -1497,13 +1531,13 @@
       <c r="B10" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="5">
         <v>132</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="5">
         <v>378.1</v>
       </c>
     </row>
@@ -1514,13 +1548,13 @@
       <c r="B11" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="5">
         <v>108</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="5">
         <v>462</v>
       </c>
     </row>
@@ -1531,13 +1565,13 @@
       <c r="B12" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="5">
         <v>107</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="5">
         <v>464.65</v>
       </c>
     </row>
@@ -1548,13 +1582,13 @@
       <c r="B13" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="5">
         <v>3602</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="5">
         <v>27.73</v>
       </c>
     </row>
@@ -1565,13 +1599,13 @@
       <c r="B14" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="5">
         <v>77</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="5">
         <v>646.65</v>
       </c>
     </row>
@@ -1582,13 +1616,13 @@
       <c r="B15" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="5">
         <v>42</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="5">
         <v>1171.9000000000001</v>
       </c>
     </row>
@@ -1599,14 +1633,99 @@
       <c r="B16" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="5">
         <v>248</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="5">
         <v>400.47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="3">
+        <v>18</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="3">
+        <v>41</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1199.2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="3">
+        <v>19</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="3">
+        <v>59</v>
+      </c>
+      <c r="E18" s="3">
+        <v>842.4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="3">
+        <v>20</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" s="3">
+        <v>11</v>
+      </c>
+      <c r="E19" s="3">
+        <v>4374.8999999999996</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="3">
+        <v>21</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" s="3">
+        <v>29</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1695.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="3">
+        <v>22</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D21" s="3">
+        <v>34</v>
+      </c>
+      <c r="E21" s="3">
+        <v>1461.22</v>
       </c>
     </row>
   </sheetData>

--- a/ETF Summary Report.xlsx
+++ b/ETF Summary Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manthan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D1A5D04-71DB-064C-B751-3884CBF7AE9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0483455-CBD9-4A43-9100-5958D6568C93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="42">
   <si>
     <t>SR. NO.</t>
   </si>
@@ -155,6 +155,12 @@
   </si>
   <si>
     <t>TECH MAHINDRA</t>
+  </si>
+  <si>
+    <t>ITIETF</t>
+  </si>
+  <si>
+    <t>PERSISTENT</t>
   </si>
 </sst>
 </file>
@@ -221,7 +227,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -231,6 +237,7 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1361,7 +1368,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="1" customWidth="1"/>
@@ -1477,17 +1484,17 @@
       <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D7" s="5">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="E7" s="5">
-        <v>1169.3</v>
+        <v>1172.02</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1654,10 +1661,10 @@
         <v>32</v>
       </c>
       <c r="D17" s="3">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="E17" s="3">
-        <v>1199.2</v>
+        <v>1197.69</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1688,10 +1695,10 @@
         <v>34</v>
       </c>
       <c r="D19" s="3">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E19" s="3">
-        <v>4374.8999999999996</v>
+        <v>4365.25</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1722,10 +1729,44 @@
         <v>36</v>
       </c>
       <c r="D21" s="3">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="E21" s="3">
-        <v>1461.22</v>
+        <v>1460.08</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="3">
+        <v>23</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="9">
+        <v>1542</v>
+      </c>
+      <c r="E22" s="9">
+        <v>32.409999999999997</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="3">
+        <v>24</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" s="9">
+        <v>8</v>
+      </c>
+      <c r="E23" s="9">
+        <v>5098.8500000000004</v>
       </c>
     </row>
   </sheetData>
